--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128490645</v>
+        <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537673</v>
+        <v>537676</v>
       </c>
       <c r="R2" t="n">
-        <v>6983478</v>
+        <v>6983471</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +779,3644 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128491087</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>537690</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6983461</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128486458</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>537634</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6983469</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128486806</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537653</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6983430</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128491030</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537703</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6983461</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128488920</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>537744</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983383</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128486547</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>537637</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6983447</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128486390</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>537633</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983475</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128490518</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>537741</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983423</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128491591</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>537648</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983480</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128490726</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>537726</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983417</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128490403</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>537705</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6983440</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128486980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>537664</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6983389</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128486624</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>537648</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6983439</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128490693</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>537698</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6983466</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128490425</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>537715</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6983436</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128489305</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>537770</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6983370</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128491480</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>537677</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6983467</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128491635</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>537646</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6983479</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128490645</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>537673</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6983478</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128490622</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>537751</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6983413</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128486238</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>537633</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6983478</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128490924</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>537689</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6983488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128490675</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>537706</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6983453</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128489739</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>537786</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6983348</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128491061</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>537690</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6983464</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128541631</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>537733</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6983284</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128541869</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>537759</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6983324</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128540315</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>537678</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6983416</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128542076</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>537772</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6983372</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128540256</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>537672</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6983414</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128542534</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>537772</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6983372</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128540913</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>537695</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6983303</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128541323</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>537633</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6983478</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128541550</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>537723</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6983307</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Matilda Ågevall</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490726</v>
+        <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537726</v>
+        <v>537770</v>
       </c>
       <c r="R12" t="n">
-        <v>6983417</v>
+        <v>6983370</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490403</v>
+        <v>128490726</v>
       </c>
       <c r="B13" t="n">
         <v>98571</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537705</v>
+        <v>537726</v>
       </c>
       <c r="R13" t="n">
-        <v>6983440</v>
+        <v>6983417</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486980</v>
+        <v>128490403</v>
       </c>
       <c r="B14" t="n">
         <v>98571</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537664</v>
+        <v>537705</v>
       </c>
       <c r="R14" t="n">
-        <v>6983389</v>
+        <v>6983440</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486624</v>
+        <v>128486980</v>
       </c>
       <c r="B15" t="n">
         <v>98571</v>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537648</v>
+        <v>537664</v>
       </c>
       <c r="R15" t="n">
-        <v>6983439</v>
+        <v>6983389</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128490693</v>
+        <v>128486624</v>
       </c>
       <c r="B16" t="n">
         <v>98571</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537698</v>
+        <v>537648</v>
       </c>
       <c r="R16" t="n">
-        <v>6983466</v>
+        <v>6983439</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490425</v>
+        <v>128490693</v>
       </c>
       <c r="B17" t="n">
         <v>98571</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537715</v>
+        <v>537698</v>
       </c>
       <c r="R17" t="n">
-        <v>6983436</v>
+        <v>6983466</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128489305</v>
+        <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537770</v>
+        <v>537715</v>
       </c>
       <c r="R18" t="n">
-        <v>6983370</v>
+        <v>6983436</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128491480</v>
+        <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537677</v>
+        <v>537673</v>
       </c>
       <c r="R19" t="n">
-        <v>6983467</v>
+        <v>6983478</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491635</v>
+        <v>128491480</v>
       </c>
       <c r="B20" t="n">
         <v>98571</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537646</v>
+        <v>537677</v>
       </c>
       <c r="R20" t="n">
-        <v>6983479</v>
+        <v>6983467</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490645</v>
+        <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537673</v>
+        <v>537646</v>
       </c>
       <c r="R21" t="n">
-        <v>6983478</v>
+        <v>6983479</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,48 +2922,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486238</v>
+        <v>128490675</v>
       </c>
       <c r="B23" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537633</v>
+        <v>537706</v>
       </c>
       <c r="R23" t="n">
-        <v>6983478</v>
+        <v>6983453</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,48 +3136,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490675</v>
+        <v>128486238</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>57845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537706</v>
+        <v>537633</v>
       </c>
       <c r="R25" t="n">
-        <v>6983453</v>
+        <v>6983478</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B28" t="n">
-        <v>80188</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R28" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R29" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490675</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>80188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537706</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983453</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>80188</v>
+        <v>57845</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,48 +3136,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128486238</v>
+        <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>57845</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537633</v>
+        <v>537706</v>
       </c>
       <c r="R25" t="n">
-        <v>6983478</v>
+        <v>6983453</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128489305</v>
+        <v>128490726</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537770</v>
+        <v>537726</v>
       </c>
       <c r="R12" t="n">
-        <v>6983370</v>
+        <v>6983417</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490726</v>
+        <v>128490403</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537726</v>
+        <v>537705</v>
       </c>
       <c r="R13" t="n">
-        <v>6983417</v>
+        <v>6983440</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128490403</v>
+        <v>128486980</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537705</v>
+        <v>537664</v>
       </c>
       <c r="R14" t="n">
-        <v>6983440</v>
+        <v>6983389</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486980</v>
+        <v>128486624</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537664</v>
+        <v>537648</v>
       </c>
       <c r="R15" t="n">
-        <v>6983389</v>
+        <v>6983439</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486624</v>
+        <v>128490693</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537648</v>
+        <v>537698</v>
       </c>
       <c r="R16" t="n">
-        <v>6983439</v>
+        <v>6983466</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490693</v>
+        <v>128490425</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537698</v>
+        <v>537715</v>
       </c>
       <c r="R17" t="n">
-        <v>6983466</v>
+        <v>6983436</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490425</v>
+        <v>128489305</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537715</v>
+        <v>537770</v>
       </c>
       <c r="R18" t="n">
-        <v>6983436</v>
+        <v>6983370</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>80192</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R28" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>80188</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R29" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>128542534</v>
       </c>
       <c r="B33" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>128541323</v>
       </c>
       <c r="B35" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490726</v>
+        <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537726</v>
+        <v>537770</v>
       </c>
       <c r="R12" t="n">
-        <v>6983417</v>
+        <v>6983370</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490403</v>
+        <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537705</v>
+        <v>537726</v>
       </c>
       <c r="R13" t="n">
-        <v>6983440</v>
+        <v>6983417</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486980</v>
+        <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537664</v>
+        <v>537705</v>
       </c>
       <c r="R14" t="n">
-        <v>6983389</v>
+        <v>6983440</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486624</v>
+        <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537648</v>
+        <v>537664</v>
       </c>
       <c r="R15" t="n">
-        <v>6983439</v>
+        <v>6983389</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128490693</v>
+        <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537698</v>
+        <v>537648</v>
       </c>
       <c r="R16" t="n">
-        <v>6983466</v>
+        <v>6983439</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490425</v>
+        <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537715</v>
+        <v>537698</v>
       </c>
       <c r="R17" t="n">
-        <v>6983436</v>
+        <v>6983466</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128489305</v>
+        <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537770</v>
+        <v>537715</v>
       </c>
       <c r="R18" t="n">
-        <v>6983370</v>
+        <v>6983436</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -3029,48 +3029,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128486238</v>
+        <v>128490675</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537633</v>
+        <v>537706</v>
       </c>
       <c r="R24" t="n">
-        <v>6983478</v>
+        <v>6983453</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,48 +3136,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490675</v>
+        <v>128486238</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537706</v>
+        <v>537633</v>
       </c>
       <c r="R25" t="n">
-        <v>6983453</v>
+        <v>6983478</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B23" t="n">
-        <v>80192</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R23" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3032,7 +3032,7 @@
         <v>128490675</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,37 +3147,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R25" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,48 +3029,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490675</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537706</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983453</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490924</v>
+        <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537689</v>
+        <v>537706</v>
       </c>
       <c r="R25" t="n">
-        <v>6983488</v>
+        <v>6983453</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490924</v>
+        <v>128490675</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537689</v>
+        <v>537706</v>
       </c>
       <c r="R23" t="n">
-        <v>6983488</v>
+        <v>6983453</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490675</v>
+        <v>128490924</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537706</v>
+        <v>537689</v>
       </c>
       <c r="R25" t="n">
-        <v>6983453</v>
+        <v>6983488</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490675</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537706</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983453</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490924</v>
+        <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>80194</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537689</v>
+        <v>537706</v>
       </c>
       <c r="R25" t="n">
-        <v>6983488</v>
+        <v>6983453</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486458</v>
+        <v>128486806</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537634</v>
+        <v>537653</v>
       </c>
       <c r="R4" t="n">
-        <v>6983469</v>
+        <v>6983430</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486806</v>
+        <v>128486458</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537653</v>
+        <v>537634</v>
       </c>
       <c r="R5" t="n">
-        <v>6983430</v>
+        <v>6983469</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128490645</v>
+        <v>128491480</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537673</v>
+        <v>537677</v>
       </c>
       <c r="R19" t="n">
-        <v>6983478</v>
+        <v>6983467</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491480</v>
+        <v>128491635</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537677</v>
+        <v>537646</v>
       </c>
       <c r="R20" t="n">
-        <v>6983467</v>
+        <v>6983479</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128491635</v>
+        <v>128490622</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537646</v>
+        <v>537751</v>
       </c>
       <c r="R21" t="n">
-        <v>6983479</v>
+        <v>6983413</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490622</v>
+        <v>128490645</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537751</v>
+        <v>537673</v>
       </c>
       <c r="R22" t="n">
-        <v>6983413</v>
+        <v>6983478</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R23" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>80221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R24" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>128542534</v>
       </c>
       <c r="B33" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>128541323</v>
       </c>
       <c r="B35" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -2494,32 +2494,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128491480</v>
+        <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537677</v>
+        <v>537673</v>
       </c>
       <c r="R19" t="n">
-        <v>6983467</v>
+        <v>6983478</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491635</v>
+        <v>128491480</v>
       </c>
       <c r="B20" t="n">
         <v>98619</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537646</v>
+        <v>537677</v>
       </c>
       <c r="R20" t="n">
-        <v>6983479</v>
+        <v>6983467</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128490622</v>
+        <v>128491635</v>
       </c>
       <c r="B21" t="n">
         <v>98619</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537751</v>
+        <v>537646</v>
       </c>
       <c r="R21" t="n">
-        <v>6983413</v>
+        <v>6983479</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,32 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490645</v>
+        <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537673</v>
+        <v>537751</v>
       </c>
       <c r="R22" t="n">
-        <v>6983478</v>
+        <v>6983413</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486806</v>
+        <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537653</v>
+        <v>537634</v>
       </c>
       <c r="R4" t="n">
-        <v>6983430</v>
+        <v>6983469</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486458</v>
+        <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537634</v>
+        <v>537653</v>
       </c>
       <c r="R5" t="n">
-        <v>6983469</v>
+        <v>6983430</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>80221</v>
+        <v>57876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128491164</v>
+        <v>128491087</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537676</v>
+        <v>537690</v>
       </c>
       <c r="R2" t="n">
-        <v>6983471</v>
+        <v>6983461</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128491087</v>
+        <v>128491164</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537690</v>
+        <v>537676</v>
       </c>
       <c r="R3" t="n">
-        <v>6983461</v>
+        <v>6983471</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128489305</v>
+        <v>128490403</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537770</v>
+        <v>537705</v>
       </c>
       <c r="R12" t="n">
-        <v>6983370</v>
+        <v>6983440</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490726</v>
+        <v>128486980</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537726</v>
+        <v>537664</v>
       </c>
       <c r="R13" t="n">
-        <v>6983417</v>
+        <v>6983389</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128490403</v>
+        <v>128486624</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537705</v>
+        <v>537648</v>
       </c>
       <c r="R14" t="n">
-        <v>6983440</v>
+        <v>6983439</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486980</v>
+        <v>128490425</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537664</v>
+        <v>537715</v>
       </c>
       <c r="R15" t="n">
-        <v>6983389</v>
+        <v>6983436</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486624</v>
+        <v>128489305</v>
       </c>
       <c r="B16" t="n">
-        <v>98625</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537648</v>
+        <v>537770</v>
       </c>
       <c r="R16" t="n">
-        <v>6983439</v>
+        <v>6983370</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490693</v>
+        <v>128490726</v>
       </c>
       <c r="B17" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537698</v>
+        <v>537726</v>
       </c>
       <c r="R17" t="n">
-        <v>6983466</v>
+        <v>6983417</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490425</v>
+        <v>128490693</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537715</v>
+        <v>537698</v>
       </c>
       <c r="R18" t="n">
-        <v>6983436</v>
+        <v>6983466</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,7 +2604,7 @@
         <v>128491480</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128491635</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128491087</v>
+        <v>128491164</v>
       </c>
       <c r="B2" t="n">
         <v>98632</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537690</v>
+        <v>537676</v>
       </c>
       <c r="R2" t="n">
-        <v>6983461</v>
+        <v>6983471</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128491164</v>
+        <v>128491087</v>
       </c>
       <c r="B3" t="n">
         <v>98632</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537676</v>
+        <v>537690</v>
       </c>
       <c r="R3" t="n">
-        <v>6983471</v>
+        <v>6983461</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490403</v>
+        <v>128490726</v>
       </c>
       <c r="B12" t="n">
         <v>98632</v>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537705</v>
+        <v>537726</v>
       </c>
       <c r="R12" t="n">
-        <v>6983440</v>
+        <v>6983417</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128490425</v>
+        <v>128489305</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537715</v>
+        <v>537770</v>
       </c>
       <c r="R15" t="n">
-        <v>6983436</v>
+        <v>6983370</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128489305</v>
+        <v>128490403</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537770</v>
+        <v>537705</v>
       </c>
       <c r="R16" t="n">
-        <v>6983370</v>
+        <v>6983440</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490726</v>
+        <v>128490693</v>
       </c>
       <c r="B17" t="n">
         <v>98632</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537726</v>
+        <v>537698</v>
       </c>
       <c r="R17" t="n">
-        <v>6983417</v>
+        <v>6983466</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490693</v>
+        <v>128490425</v>
       </c>
       <c r="B18" t="n">
         <v>98632</v>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537698</v>
+        <v>537715</v>
       </c>
       <c r="R18" t="n">
-        <v>6983466</v>
+        <v>6983436</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>57876</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R23" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B24" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R24" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B28" t="n">
-        <v>80225</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R28" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R29" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>57876</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>80225</v>
+        <v>57876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128491164</v>
+        <v>128491087</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537676</v>
+        <v>537690</v>
       </c>
       <c r="R2" t="n">
-        <v>6983471</v>
+        <v>6983461</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128491087</v>
+        <v>128491164</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537690</v>
+        <v>537676</v>
       </c>
       <c r="R3" t="n">
-        <v>6983461</v>
+        <v>6983471</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490726</v>
+        <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537726</v>
+        <v>537770</v>
       </c>
       <c r="R12" t="n">
-        <v>6983417</v>
+        <v>6983370</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128486980</v>
+        <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537664</v>
+        <v>537726</v>
       </c>
       <c r="R13" t="n">
-        <v>6983389</v>
+        <v>6983417</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486624</v>
+        <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537648</v>
+        <v>537705</v>
       </c>
       <c r="R14" t="n">
-        <v>6983439</v>
+        <v>6983440</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128489305</v>
+        <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537770</v>
+        <v>537664</v>
       </c>
       <c r="R15" t="n">
-        <v>6983370</v>
+        <v>6983389</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128490403</v>
+        <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537705</v>
+        <v>537648</v>
       </c>
       <c r="R16" t="n">
-        <v>6983440</v>
+        <v>6983439</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2283,7 @@
         <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491480</v>
+        <v>128491635</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537677</v>
+        <v>537646</v>
       </c>
       <c r="R20" t="n">
-        <v>6983467</v>
+        <v>6983479</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128491635</v>
+        <v>128491480</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537646</v>
+        <v>537677</v>
       </c>
       <c r="R21" t="n">
-        <v>6983479</v>
+        <v>6983467</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>128490622</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>57880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R23" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B24" t="n">
-        <v>57876</v>
+        <v>80229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R24" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>128541869</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541631</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>128542534</v>
       </c>
       <c r="B33" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>128541323</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128491087</v>
+        <v>128491164</v>
       </c>
       <c r="B2" t="n">
         <v>98636</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537690</v>
+        <v>537676</v>
       </c>
       <c r="R2" t="n">
-        <v>6983461</v>
+        <v>6983471</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128491164</v>
+        <v>128491087</v>
       </c>
       <c r="B3" t="n">
         <v>98636</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537676</v>
+        <v>537690</v>
       </c>
       <c r="R3" t="n">
-        <v>6983471</v>
+        <v>6983461</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486458</v>
+        <v>128486806</v>
       </c>
       <c r="B4" t="n">
         <v>98636</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537634</v>
+        <v>537653</v>
       </c>
       <c r="R4" t="n">
-        <v>6983469</v>
+        <v>6983430</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486806</v>
+        <v>128486458</v>
       </c>
       <c r="B5" t="n">
         <v>98636</v>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537653</v>
+        <v>537634</v>
       </c>
       <c r="R5" t="n">
-        <v>6983430</v>
+        <v>6983469</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486547</v>
+        <v>128486390</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537637</v>
+        <v>537633</v>
       </c>
       <c r="R8" t="n">
-        <v>6983447</v>
+        <v>6983475</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486390</v>
+        <v>128486547</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537633</v>
+        <v>537637</v>
       </c>
       <c r="R9" t="n">
-        <v>6983475</v>
+        <v>6983447</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128489305</v>
+        <v>128490726</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537770</v>
+        <v>537726</v>
       </c>
       <c r="R12" t="n">
-        <v>6983370</v>
+        <v>6983417</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490726</v>
+        <v>128486980</v>
       </c>
       <c r="B13" t="n">
         <v>98636</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537726</v>
+        <v>537664</v>
       </c>
       <c r="R13" t="n">
-        <v>6983417</v>
+        <v>6983389</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128490403</v>
+        <v>128490693</v>
       </c>
       <c r="B14" t="n">
         <v>98636</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537705</v>
+        <v>537698</v>
       </c>
       <c r="R14" t="n">
-        <v>6983440</v>
+        <v>6983466</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486980</v>
+        <v>128490403</v>
       </c>
       <c r="B15" t="n">
         <v>98636</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537664</v>
+        <v>537705</v>
       </c>
       <c r="R15" t="n">
-        <v>6983389</v>
+        <v>6983440</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490693</v>
+        <v>128490425</v>
       </c>
       <c r="B17" t="n">
         <v>98636</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537698</v>
+        <v>537715</v>
       </c>
       <c r="R17" t="n">
-        <v>6983466</v>
+        <v>6983436</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128490425</v>
+        <v>128489305</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537715</v>
+        <v>537770</v>
       </c>
       <c r="R18" t="n">
-        <v>6983436</v>
+        <v>6983370</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491635</v>
+        <v>128491480</v>
       </c>
       <c r="B20" t="n">
         <v>98636</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537646</v>
+        <v>537677</v>
       </c>
       <c r="R20" t="n">
-        <v>6983479</v>
+        <v>6983467</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128491480</v>
+        <v>128491635</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537677</v>
+        <v>537646</v>
       </c>
       <c r="R21" t="n">
-        <v>6983467</v>
+        <v>6983479</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128486238</v>
+        <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>57880</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,37 +2933,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537633</v>
+        <v>537689</v>
       </c>
       <c r="R23" t="n">
-        <v>6983478</v>
+        <v>6983488</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490924</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>57880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,37 +3040,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537689</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983488</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R28" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R29" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128486806</v>
+        <v>128486458</v>
       </c>
       <c r="B4" t="n">
         <v>98636</v>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537653</v>
+        <v>537634</v>
       </c>
       <c r="R4" t="n">
-        <v>6983430</v>
+        <v>6983469</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128486458</v>
+        <v>128486806</v>
       </c>
       <c r="B5" t="n">
         <v>98636</v>
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537634</v>
+        <v>537653</v>
       </c>
       <c r="R5" t="n">
-        <v>6983469</v>
+        <v>6983430</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128486390</v>
+        <v>128486547</v>
       </c>
       <c r="B8" t="n">
         <v>98636</v>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537633</v>
+        <v>537637</v>
       </c>
       <c r="R8" t="n">
-        <v>6983475</v>
+        <v>6983447</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128486547</v>
+        <v>128486390</v>
       </c>
       <c r="B9" t="n">
         <v>98636</v>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537637</v>
+        <v>537633</v>
       </c>
       <c r="R9" t="n">
-        <v>6983447</v>
+        <v>6983475</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128486980</v>
+        <v>128490403</v>
       </c>
       <c r="B13" t="n">
         <v>98636</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537664</v>
+        <v>537705</v>
       </c>
       <c r="R13" t="n">
-        <v>6983389</v>
+        <v>6983440</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128490693</v>
+        <v>128486980</v>
       </c>
       <c r="B14" t="n">
         <v>98636</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537698</v>
+        <v>537664</v>
       </c>
       <c r="R14" t="n">
-        <v>6983466</v>
+        <v>6983389</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128490403</v>
+        <v>128486624</v>
       </c>
       <c r="B15" t="n">
         <v>98636</v>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537705</v>
+        <v>537648</v>
       </c>
       <c r="R15" t="n">
-        <v>6983440</v>
+        <v>6983439</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128486624</v>
+        <v>128490693</v>
       </c>
       <c r="B16" t="n">
         <v>98636</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537648</v>
+        <v>537698</v>
       </c>
       <c r="R16" t="n">
-        <v>6983439</v>
+        <v>6983466</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3029,48 +3029,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128486238</v>
+        <v>128490675</v>
       </c>
       <c r="B24" t="n">
-        <v>57880</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537633</v>
+        <v>537706</v>
       </c>
       <c r="R24" t="n">
-        <v>6983478</v>
+        <v>6983453</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,48 +3136,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128490675</v>
+        <v>128486238</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>57880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537706</v>
+        <v>537633</v>
       </c>
       <c r="R25" t="n">
-        <v>6983453</v>
+        <v>6983478</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128491164</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128491087</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128486458</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128486806</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128491030</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128488920</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128486547</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>128486390</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>128490518</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>128491591</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128490726</v>
+        <v>128489305</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537726</v>
+        <v>537770</v>
       </c>
       <c r="R12" t="n">
-        <v>6983417</v>
+        <v>6983370</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128490403</v>
+        <v>128490726</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537705</v>
+        <v>537726</v>
       </c>
       <c r="R13" t="n">
-        <v>6983440</v>
+        <v>6983417</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128486980</v>
+        <v>128490403</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537664</v>
+        <v>537705</v>
       </c>
       <c r="R14" t="n">
-        <v>6983389</v>
+        <v>6983440</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128486624</v>
+        <v>128486980</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537648</v>
+        <v>537664</v>
       </c>
       <c r="R15" t="n">
-        <v>6983439</v>
+        <v>6983389</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128490693</v>
+        <v>128486624</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537698</v>
+        <v>537648</v>
       </c>
       <c r="R16" t="n">
-        <v>6983466</v>
+        <v>6983439</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128490425</v>
+        <v>128490693</v>
       </c>
       <c r="B17" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537715</v>
+        <v>537698</v>
       </c>
       <c r="R17" t="n">
-        <v>6983436</v>
+        <v>6983466</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128489305</v>
+        <v>128490425</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537770</v>
+        <v>537715</v>
       </c>
       <c r="R18" t="n">
-        <v>6983370</v>
+        <v>6983436</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
         <v>128490645</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128491480</v>
+        <v>128491635</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537677</v>
+        <v>537646</v>
       </c>
       <c r="R20" t="n">
-        <v>6983467</v>
+        <v>6983479</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128491635</v>
+        <v>128490622</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537646</v>
+        <v>537751</v>
       </c>
       <c r="R21" t="n">
-        <v>6983479</v>
+        <v>6983413</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128490622</v>
+        <v>128491480</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537751</v>
+        <v>537677</v>
       </c>
       <c r="R22" t="n">
-        <v>6983413</v>
+        <v>6983467</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,7 +2925,7 @@
         <v>128490924</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,48 +3029,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128490675</v>
+        <v>128486238</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537706</v>
+        <v>537633</v>
       </c>
       <c r="R24" t="n">
-        <v>6983453</v>
+        <v>6983478</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,48 +3136,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128486238</v>
+        <v>128490675</v>
       </c>
       <c r="B25" t="n">
-        <v>57880</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nörder-Kroktjärnberget, Jmt</t>
+          <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537633</v>
+        <v>537706</v>
       </c>
       <c r="R25" t="n">
-        <v>6983478</v>
+        <v>6983453</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3246,7 +3246,7 @@
         <v>128489739</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>128491061</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>128542534</v>
       </c>
       <c r="B33" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>128541323</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -3460,7 +3460,7 @@
         <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B28" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R28" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R29" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38619-2025 artfynd.xlsx
+++ b/artfynd/A 38619-2025 artfynd.xlsx
@@ -3457,32 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128541869</v>
+        <v>128541631</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537759</v>
+        <v>537733</v>
       </c>
       <c r="R28" t="n">
-        <v>6983324</v>
+        <v>6983284</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128541631</v>
+        <v>128541869</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537733</v>
+        <v>537759</v>
       </c>
       <c r="R29" t="n">
-        <v>6983284</v>
+        <v>6983324</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
         <v>128540315</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>128542076</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>128540256</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>128540913</v>
       </c>
       <c r="B34" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>128541550</v>
       </c>
       <c r="B36" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
